--- a/dataset/adult_income_female/adult_dataset_female.xlsx
+++ b/dataset/adult_income_female/adult_dataset_female.xlsx
@@ -18,13 +18,13 @@
     <t>age</t>
   </si>
   <si>
-    <t>education-num</t>
+    <t>education</t>
   </si>
   <si>
     <t>hours-per-week</t>
   </si>
   <si>
-    <t>income_high</t>
+    <t>income</t>
   </si>
 </sst>
 </file>
